--- a/src/nodes/HPC/compressor_stage_9_blade_stator_coordinates_lattice.xlsx
+++ b/src/nodes/HPC/compressor_stage_9_blade_stator_coordinates_lattice.xlsx
@@ -346,10 +346,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>8.2196256805523</v>
+        <v>8.0566670652540147</v>
       </c>
       <c r="B1">
-        <v>8.7932131373716658</v>
+        <v>8.9427601671571075</v>
       </c>
       <c r="C1">
         <v>194.11826296981104</v>
@@ -357,10 +357,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>7.4964033471596068</v>
+        <v>7.3366271803883487</v>
       </c>
       <c r="B2">
-        <v>8.6266589749073557</v>
+        <v>8.7629452713481175</v>
       </c>
       <c r="C2">
         <v>194.11826296981104</v>
@@ -368,10 +368,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>6.8385165854801624</v>
+        <v>6.6833449658574144</v>
       </c>
       <c r="B3">
-        <v>8.38210929756263</v>
+        <v>8.5063485370352367</v>
       </c>
       <c r="C3">
         <v>194.11826296981104</v>
@@ -379,10 +379,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>6.1954320830508</v>
+        <v>6.0451871975862179</v>
       </c>
       <c r="B4">
-        <v>8.1198891567731089</v>
+        <v>8.2323563066789323</v>
       </c>
       <c r="C4">
         <v>194.11826296981104</v>
@@ -390,10 +390,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>5.5642727716679516</v>
+        <v>5.4192141849035371</v>
       </c>
       <c r="B5">
-        <v>7.8434331044987644</v>
+        <v>7.9443496876970849</v>
       </c>
       <c r="C5">
         <v>194.11826296981104</v>
@@ -401,10 +401,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>4.9438278153526651</v>
+        <v>4.804188736689853</v>
       </c>
       <c r="B6">
-        <v>7.5541865979865088</v>
+        <v>7.6437516447956391</v>
       </c>
       <c r="C6">
         <v>194.11826296981104</v>
@@ -412,10 +412,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>4.3333834654626271</v>
+        <v>4.1993815688000051</v>
       </c>
       <c r="B7">
-        <v>7.2530016875267522</v>
+        <v>7.3314009696396774</v>
       </c>
       <c r="C7">
         <v>194.11826296981104</v>
@@ -423,10 +423,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>3.7324979409546435</v>
+        <v>3.604341284353731</v>
       </c>
       <c r="B8">
-        <v>6.9404057571925915</v>
+        <v>7.00781683975873</v>
       </c>
       <c r="C8">
         <v>194.11826296981104</v>
@@ -434,10 +434,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>3.1405198187555823</v>
+        <v>3.0184022813577465</v>
       </c>
       <c r="B9">
-        <v>6.6171764550042687</v>
+        <v>6.6737648023101475</v>
       </c>
       <c r="C9">
         <v>194.11826296981104</v>
@@ -445,10 +445,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>2.5567529683592904</v>
+        <v>2.4408532772806351</v>
       </c>
       <c r="B10">
-        <v>6.284144799284995</v>
+        <v>6.33006294426707</v>
       </c>
       <c r="C10">
         <v>194.11826296981104</v>
@@ -456,10 +456,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>1.9805320715574628</v>
+        <v>1.8710144725514593</v>
       </c>
       <c r="B11">
-        <v>5.9421050256227552</v>
+        <v>5.9774931422379636</v>
       </c>
       <c r="C11">
         <v>194.11826296981104</v>
@@ -467,10 +467,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>1.4114848784580305</v>
+        <v>1.3085055148609743</v>
       </c>
       <c r="B12">
-        <v>5.5915015140273168</v>
+        <v>5.6164928613026719</v>
       </c>
       <c r="C12">
         <v>194.11826296981104</v>
@@ -478,10 +478,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>0.8503806001359947</v>
+        <v>0.75411235798621523</v>
       </c>
       <c r="B13">
-        <v>5.2314160049308356</v>
+        <v>5.2461581307912</v>
       </c>
       <c r="C13">
         <v>194.11826296981104</v>
@@ -489,10 +489,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>0.29766815857036349</v>
+        <v>0.2082936951733694</v>
       </c>
       <c r="B14">
-        <v>4.8613125896395344</v>
+        <v>4.8659613812036717</v>
       </c>
       <c r="C14">
         <v>194.11826296981104</v>
@@ -500,10 +500,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-0.24862614161089539</v>
+        <v>-0.330967128541043</v>
       </c>
       <c r="B15">
-        <v>4.4835474025335413</v>
+        <v>4.4782220834705022</v>
       </c>
       <c r="C15">
         <v>194.11826296981104</v>
@@ -511,10 +511,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-0.79031243647366256</v>
+        <v>-0.86551964877105847</v>
       </c>
       <c r="B16">
-        <v>4.100281326126928</v>
+        <v>4.0850674949407342</v>
       </c>
       <c r="C16">
         <v>194.11826296981104</v>
@@ -522,10 +522,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-1.3261240075081791</v>
+        <v>-1.3940695755232795</v>
       </c>
       <c r="B17">
-        <v>3.7100021923956459</v>
+        <v>3.68500897820757</v>
       </c>
       <c r="C17">
         <v>194.11826296981104</v>
@@ -533,10 +533,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-1.8544162765502388</v>
+        <v>-1.9149365346302048</v>
       </c>
       <c r="B18">
-        <v>3.3107467565510706</v>
+        <v>3.2761138382367525</v>
       </c>
       <c r="C18">
         <v>194.11826296981104</v>
@@ -544,10 +544,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-2.3751100813935127</v>
+        <v>-2.4280396408353897</v>
       </c>
       <c r="B19">
-        <v>2.9024205172843471</v>
+        <v>2.8582890442399607</v>
       </c>
       <c r="C19">
         <v>194.11826296981104</v>
@@ -555,10 +555,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-2.8885176138211475</v>
+        <v>-2.9336978811101568</v>
       </c>
       <c r="B20">
-        <v>2.4853961591565641</v>
+        <v>2.4319014814903563</v>
       </c>
       <c r="C20">
         <v>194.11826296981104</v>
@@ -566,10 +566,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-3.3949510656162789</v>
+        <v>-3.4322302424258204</v>
       </c>
       <c r="B21">
-        <v>2.060046366728816</v>
+        <v>1.9973180352611089</v>
       </c>
       <c r="C21">
         <v>194.11826296981104</v>
@@ -577,10 +577,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-3.8946659411933631</v>
+        <v>-3.9238977905237826</v>
       </c>
       <c r="B22">
-        <v>1.6266761529953526</v>
+        <v>1.5548389722855296</v>
       </c>
       <c r="C22">
         <v>194.11826296981104</v>
@@ -588,10 +588,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-4.3876909954921084</v>
+        <v>-4.40872990622578</v>
       </c>
       <c r="B23">
-        <v>1.1853198446830844</v>
+        <v>1.1044980851375381</v>
       </c>
       <c r="C23">
         <v>194.11826296981104</v>
@@ -599,10 +599,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-4.8739982960835277</v>
+        <v>-4.8866980491236225</v>
       </c>
       <c r="B24">
-        <v>0.73594409695208618</v>
+        <v>0.64626254785120574</v>
       </c>
       <c r="C24">
         <v>194.11826296981104</v>
@@ -610,10 +610,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-5.35355991053864</v>
+        <v>-5.35777367880913</v>
       </c>
       <c r="B25">
-        <v>0.27851556496242841</v>
+        <v>0.180099534460599</v>
       </c>
       <c r="C25">
         <v>194.11826296981104</v>
@@ -621,10 +621,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-5.8263365530088054</v>
+        <v>-5.8219166543351308</v>
       </c>
       <c r="B26">
-        <v>-0.18701264947490731</v>
+        <v>-0.29403712344769439</v>
       </c>
       <c r="C26">
         <v>194.11826296981104</v>
@@ -632,10 +632,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-6.2922435239667722</v>
+        <v>-6.2790404325985438</v>
       </c>
       <c r="B27">
-        <v>-0.66074165794532524</v>
+        <v>-0.77624696407703608</v>
       </c>
       <c r="C27">
         <v>194.11826296981104</v>
@@ -643,10 +643,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-6.7511847704656134</v>
+        <v>-6.7290468699572852</v>
       </c>
       <c r="B28">
-        <v>-1.1427861253833116</v>
+        <v>-1.2666428680782578</v>
       </c>
       <c r="C28">
         <v>194.11826296981104</v>
@@ -654,10 +654,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-7.2030642395584188</v>
+        <v>-7.1718378227692847</v>
       </c>
       <c r="B29">
-        <v>-1.6332607167233613</v>
+        <v>-1.7653377161022028</v>
       </c>
       <c r="C29">
         <v>194.11826296981104</v>
@@ -665,10 +665,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-7.6478236840358838</v>
+        <v>-7.60735377601241</v>
       </c>
       <c r="B30">
-        <v>-2.132234965620122</v>
+        <v>-2.272399959800866</v>
       </c>
       <c r="C30">
         <v>194.11826296981104</v>
@@ -676,10 +676,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-8.08555607963917</v>
+        <v>-8.0356897291443037</v>
       </c>
       <c r="B31">
-        <v>-2.6395978806088642</v>
+        <v>-2.7877203348308628</v>
       </c>
       <c r="C31">
         <v>194.11826296981104</v>
@@ -687,10 +687,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-8.51639220784706</v>
+        <v>-8.4569793102425574</v>
       </c>
       <c r="B32">
-        <v>-3.1551933389450206</v>
+        <v>-3.3111451478499765</v>
       </c>
       <c r="C32">
         <v>194.11826296981104</v>
@@ -698,10 +698,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-8.9404628501383279</v>
+        <v>-8.87135614738476</v>
       </c>
       <c r="B33">
-        <v>-3.6788652178840198</v>
+        <v>-3.84252070551598</v>
       </c>
       <c r="C33">
         <v>194.11826296981104</v>
@@ -709,10 +709,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-9.3578304725854888</v>
+        <v>-9.2788840662843235</v>
       </c>
       <c r="B34">
-        <v>-4.2105389474272963</v>
+        <v>-4.3817735982027441</v>
       </c>
       <c r="C34">
         <v>194.11826296981104</v>
@@ -720,10 +720,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-9.768284279636033</v>
+        <v>-9.6793476831980048</v>
       </c>
       <c r="B35">
-        <v>-4.7504661685603295</v>
+        <v>-4.9291515511485473</v>
       </c>
       <c r="C35">
         <v>194.11826296981104</v>
@@ -731,10 +731,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-10.171545160331185</v>
+        <v>-10.072461812018391</v>
       </c>
       <c r="B36">
-        <v>-5.29898007501461</v>
+        <v>-5.4849825733077591</v>
       </c>
       <c r="C36">
         <v>194.11826296981104</v>
@@ -742,10 +742,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-10.567334003712178</v>
+        <v>-10.457941266638072</v>
       </c>
       <c r="B37">
-        <v>-5.8564138605216316</v>
+        <v>-6.0495946736347586</v>
       </c>
       <c r="C37">
         <v>194.11826296981104</v>
@@ -753,10 +753,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-10.955208480937214</v>
+        <v>-10.835334090454754</v>
       </c>
       <c r="B38">
-        <v>-6.4232955630989315</v>
+        <v>-6.6235076734275866</v>
       </c>
       <c r="C38">
         <v>194.11826296981104</v>
@@ -764,10 +764,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-11.334073391632414</v>
+        <v>-11.203521244886661</v>
       </c>
       <c r="B39">
-        <v>-7.00093259790824</v>
+        <v>-7.208008643358955</v>
       </c>
       <c r="C39">
         <v>194.11826296981104</v>
@@ -775,10 +775,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-11.702670317540866</v>
+        <v>-11.561216920857119</v>
       </c>
       <c r="B40">
-        <v>-7.5908272243973389</v>
+        <v>-7.8045764664452388</v>
       </c>
       <c r="C40">
         <v>194.11826296981104</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-12.059740840405659</v>
+        <v>-11.907135309289473</v>
       </c>
       <c r="B41">
-        <v>-8.1944817020140022</v>
+        <v>-8.4146900257028161</v>
       </c>
       <c r="C41">
         <v>194.11826296981104</v>
@@ -797,10 +797,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-12.059740840405659</v>
+        <v>-11.907135309289473</v>
       </c>
       <c r="B42">
-        <v>-8.1944817020140022</v>
+        <v>-8.4146900257028161</v>
       </c>
       <c r="C42">
         <v>194.11826296981104</v>
@@ -808,10 +808,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-11.646752633797865</v>
+        <v>-11.504082128900595</v>
       </c>
       <c r="B43">
-        <v>-7.6575799659758026</v>
+        <v>-7.8702904787372</v>
       </c>
       <c r="C43">
         <v>194.11826296981104</v>
@@ -819,10 +819,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-11.231841444088991</v>
+        <v>-11.099064109626029</v>
       </c>
       <c r="B44">
-        <v>-7.1229738256313651</v>
+        <v>-7.3281508060489573</v>
       </c>
       <c r="C44">
         <v>194.11826296981104</v>
@@ -830,10 +830,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-10.813899027594948</v>
+        <v>-10.690948885672176</v>
       </c>
       <c r="B45">
-        <v>-6.59198626682879</v>
+        <v>-6.7895734067040747</v>
       </c>
       <c r="C45">
         <v>194.11826296981104</v>
@@ -841,10 +841,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-10.391817140631646</v>
+        <v>-10.278604091245443</v>
       </c>
       <c r="B46">
-        <v>-6.0659402754161684</v>
+        <v>-6.2558606797685412</v>
       </c>
       <c r="C46">
         <v>194.11826296981104</v>
@@ -852,10 +852,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-9.96464446535844</v>
+        <v>-9.8610577020545573</v>
       </c>
       <c r="B47">
-        <v>-5.5459715041910576</v>
+        <v>-5.7281306063189854</v>
       </c>
       <c r="C47">
         <v>194.11826296981104</v>
@@ -863,10 +863,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-9.5320573873084964</v>
+        <v>-9.4379790598175788</v>
       </c>
       <c r="B48">
-        <v>-5.0324662737488355</v>
+        <v>-5.2067634954746005</v>
       </c>
       <c r="C48">
         <v>194.11826296981104</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-9.0938892178584219</v>
+        <v>-9.0091978477548817</v>
       </c>
       <c r="B49">
-        <v>-4.5256235716343367</v>
+        <v>-4.6919552383652166</v>
       </c>
       <c r="C49">
         <v>194.11826296981104</v>
@@ -885,10 +885,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-8.6499732683848318</v>
+        <v>-8.574543749086855</v>
       </c>
       <c r="B50">
-        <v>-4.025642385392401</v>
+        <v>-4.1839017261206735</v>
       </c>
       <c r="C50">
         <v>194.11826296981104</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-8.2002050322066271</v>
+        <v>-8.1339099824326677</v>
       </c>
       <c r="B51">
-        <v>-3.5326474717548808</v>
+        <v>-3.682725774152241</v>
       </c>
       <c r="C51">
         <v>194.11826296981104</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-7.7447287304118628</v>
+        <v>-7.6874439080066672</v>
       </c>
       <c r="B52">
-        <v>-3.0464666642016973</v>
+        <v>-3.1882578949969451</v>
       </c>
       <c r="C52">
         <v>194.11826296981104</v>
@@ -918,10 +918,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-7.2837507660308889</v>
+        <v>-7.2353564214219857</v>
       </c>
       <c r="B53">
-        <v>-2.5668535653997826</v>
+        <v>-2.7002555254732439</v>
       </c>
       <c r="C53">
         <v>194.11826296981104</v>
@@ -929,10 +929,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-6.8174775420940419</v>
+        <v>-6.77785841829175</v>
       </c>
       <c r="B54">
-        <v>-2.0935617780160651</v>
+        <v>-2.2184761023995909</v>
       </c>
       <c r="C54">
         <v>194.11826296981104</v>
@@ -940,10 +940,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-6.3460723953236142</v>
+        <v>-6.3151167905367673</v>
       </c>
       <c r="B55">
-        <v>-1.6263963158979835</v>
+        <v>-1.7427276737733703</v>
       </c>
       <c r="C55">
         <v>194.11826296981104</v>
@@ -951,10 +951,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-5.8695263972096772</v>
+        <v>-5.8471224153085384</v>
       </c>
       <c r="B56">
-        <v>-1.1653678376149956</v>
+        <v>-1.2730207323076566</v>
       </c>
       <c r="C56">
         <v>194.11826296981104</v>
@@ -962,10 +962,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-5.3877875529342427</v>
+        <v>-5.3738221660662306</v>
       </c>
       <c r="B57">
-        <v>-0.71053841291705921</v>
+        <v>-0.80941638189444254</v>
       </c>
       <c r="C57">
         <v>194.11826296981104</v>
@@ -973,10 +973,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-4.9008038676793335</v>
+        <v>-4.8951629162690269</v>
       </c>
       <c r="B58">
-        <v>-0.26197011155414335</v>
+        <v>-0.35197572642573383</v>
       </c>
       <c r="C58">
         <v>194.11826296981104</v>
@@ -984,10 +984,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-4.4085297984384049</v>
+        <v>-4.4110981316181164</v>
       </c>
       <c r="B59">
-        <v>0.18028269868985763</v>
+        <v>0.099247712323413589</v>
       </c>
       <c r="C59">
         <v>194.11826296981104</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-3.9109456094507173</v>
+        <v>-3.9216076467828103</v>
       </c>
       <c r="B60">
-        <v>0.61619645789527466</v>
+        <v>0.54423074104566838</v>
       </c>
       <c r="C60">
         <v>194.11826296981104</v>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-3.4080380167669686</v>
+        <v>-3.4266778886744382</v>
       </c>
       <c r="B61">
-        <v>1.0457553081085029</v>
+        <v>0.98295774855063511</v>
       </c>
       <c r="C61">
         <v>194.11826296981104</v>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-2.8997937364378652</v>
+        <v>-2.9262952842043388</v>
       </c>
       <c r="B62">
-        <v>1.4689433913759333</v>
+        <v>1.4154131236479155</v>
       </c>
       <c r="C62">
         <v>194.11826296981104</v>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-2.3862511892429321</v>
+        <v>-2.4204990904214094</v>
       </c>
       <c r="B63">
-        <v>1.8858065731947611</v>
+        <v>1.8416420181286604</v>
       </c>
       <c r="C63">
         <v>194.11826296981104</v>
@@ -1039,10 +1039,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-1.8676556148769832</v>
+        <v>-1.9095398849248051</v>
       </c>
       <c r="B64">
-        <v>2.2966376128653949</v>
+        <v>2.2619326357102114</v>
       </c>
       <c r="C64">
         <v>194.11826296981104</v>
@@ -1050,10 +1050,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-1.3443039577636633</v>
+        <v>-1.3937210754512557</v>
       </c>
       <c r="B65">
-        <v>2.7017909931390403</v>
+        <v>2.67663394309145</v>
       </c>
       <c r="C65">
         <v>194.11826296981104</v>
@@ -1061,10 +1061,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-0.816493162326609</v>
+        <v>-0.87334606973748152</v>
       </c>
       <c r="B66">
-        <v>3.1016211967669074</v>
+        <v>3.0860949069712653</v>
       </c>
       <c r="C66">
         <v>194.11826296981104</v>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-0.28412475262343379</v>
+        <v>-0.34831424840684971</v>
       </c>
       <c r="B67">
-        <v>3.4960106663200436</v>
+        <v>3.4901997992140243</v>
       </c>
       <c r="C67">
         <v>194.11826296981104</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>0.25448142875235</v>
+        <v>0.18309111637069608</v>
       </c>
       <c r="B68">
-        <v>3.882953683648851</v>
+        <v>3.8869741123460226</v>
       </c>
       <c r="C68">
         <v>194.11826296981104</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>0.80063363674402688</v>
+        <v>0.7222067551069945</v>
       </c>
       <c r="B69">
-        <v>4.2608884958640516</v>
+        <v>4.274880395677803</v>
       </c>
       <c r="C69">
         <v>194.11826296981104</v>
@@ -1105,10 +1105,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>1.3525708349779135</v>
+        <v>1.2672333005875403</v>
       </c>
       <c r="B70">
-        <v>4.6319173718382762</v>
+        <v>4.6559882049949461</v>
       </c>
       <c r="C70">
         <v>194.11826296981104</v>
@@ -1116,10 +1116,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>1.9083731396939279</v>
+        <v>1.8162090807281106</v>
       </c>
       <c r="B71">
-        <v>4.9983322073711891</v>
+        <v>5.032553772254218</v>
       </c>
       <c r="C71">
         <v>194.11826296981104</v>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>2.4685545689033344</v>
+        <v>2.3696593016919394</v>
       </c>
       <c r="B72">
-        <v>5.3595193842086744</v>
+        <v>5.4039730276220785</v>
       </c>
       <c r="C72">
         <v>194.11826296981104</v>
@@ -1138,10 +1138,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>3.033955005216745</v>
+        <v>2.9284421270332541</v>
       </c>
       <c r="B73">
-        <v>5.7144762773650442</v>
+        <v>5.7692589478081633</v>
       </c>
       <c r="C73">
         <v>194.11826296981104</v>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>3.6042838878708112</v>
+        <v>3.4922606716228226</v>
       </c>
       <c r="B74">
-        <v>6.0635497489821155</v>
+        <v>6.12875299748511</v>
       </c>
       <c r="C74">
         <v>194.11826296981104</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>4.1789632981187141</v>
+        <v>4.060524437693978</v>
       </c>
       <c r="B75">
-        <v>6.4074296999673939</v>
+        <v>6.4831343421170535</v>
       </c>
       <c r="C75">
         <v>194.11826296981104</v>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>4.7573963286536936</v>
+        <v>4.6326235256137887</v>
       </c>
       <c r="B76">
-        <v>6.7468286991636406</v>
+        <v>6.8331044623710726</v>
       </c>
       <c r="C76">
         <v>194.11826296981104</v>
@@ -1182,10 +1182,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>5.3390370606193827</v>
+        <v>5.208000134017901</v>
       </c>
       <c r="B77">
-        <v>7.0823984470330767</v>
+        <v>7.1793049176973476</v>
       </c>
       <c r="C77">
         <v>194.11826296981104</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>5.923562517520959</v>
+        <v>5.7863242564825246</v>
       </c>
       <c r="B78">
-        <v>7.4145245025805027</v>
+        <v>7.522115267475491</v>
       </c>
       <c r="C78">
         <v>194.11826296981104</v>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>6.510383945373011</v>
+        <v>6.3669943241618405</v>
       </c>
       <c r="B79">
-        <v>7.7439097014745482</v>
+        <v>7.8622274106548948</v>
       </c>
       <c r="C79">
         <v>194.11826296981104</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>7.0984283165227628</v>
+        <v>6.9489139538081712</v>
       </c>
       <c r="B80">
-        <v>8.0718349897919719</v>
+        <v>8.20090236070472</v>
       </c>
       <c r="C80">
         <v>194.11826296981104</v>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>7.6849667598767883</v>
+        <v>7.5292948775290931</v>
       </c>
       <c r="B81">
-        <v>8.4015580065247217</v>
+        <v>8.5413470649906849</v>
       </c>
       <c r="C81">
         <v>194.11826296981104</v>
@@ -1237,10 +1237,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>8.2196256805523</v>
+        <v>8.0566670652540147</v>
       </c>
       <c r="B82">
-        <v>8.7932131373716658</v>
+        <v>8.9427601671571075</v>
       </c>
       <c r="C82">
         <v>194.11826296981104</v>
@@ -1258,10 +1258,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>8.667102340493253</v>
+        <v>8.4743671577408541</v>
       </c>
       <c r="B1">
-        <v>10.087996045330947</v>
+        <v>10.25043552572278</v>
       </c>
       <c r="C1">
         <v>214.35566444654796</v>
@@ -1269,10 +1269,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>7.7997945728743545</v>
+        <v>7.5726431646401542</v>
       </c>
       <c r="B2">
-        <v>9.9572619920860035</v>
+        <v>10.142650915204367</v>
       </c>
       <c r="C2">
         <v>214.35566444654796</v>
@@ -1280,10 +1280,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>7.0533029014068527</v>
+        <v>6.81727117711218</v>
       </c>
       <c r="B3">
-        <v>9.693194694334089</v>
+        <v>9.879378081769552</v>
       </c>
       <c r="C3">
         <v>214.35566444654796</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>6.3304086408543778</v>
+        <v>6.089190175945614</v>
       </c>
       <c r="B4">
-        <v>9.4030851765511461</v>
+        <v>9.5871105860862418</v>
       </c>
       <c r="C4">
         <v>214.35566444654796</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>5.6256237113557814</v>
+        <v>5.3816968134738854</v>
       </c>
       <c r="B5">
-        <v>9.0929901109630578</v>
+        <v>9.2729702411571786</v>
       </c>
       <c r="C5">
         <v>214.35566444654796</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>4.9366639633148459</v>
+        <v>4.6920108375989678</v>
       </c>
       <c r="B6">
-        <v>8.7654302964228332</v>
+        <v>8.9399108599915582</v>
       </c>
       <c r="C6">
         <v>214.35566444654796</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>4.2621978475035087</v>
+        <v>4.0185171696365165</v>
       </c>
       <c r="B7">
-        <v>8.4218752372800871</v>
+        <v>8.589648344694826</v>
       </c>
       <c r="C7">
         <v>214.35566444654796</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>3.6014152679146769</v>
+        <v>3.3602386542914346</v>
       </c>
       <c r="B8">
-        <v>8.0632189595166928</v>
+        <v>8.2232208507726359</v>
       </c>
       <c r="C8">
         <v>214.35566444654796</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>2.9530981414807633</v>
+        <v>2.7156966940626877</v>
       </c>
       <c r="B9">
-        <v>7.6908057456633285</v>
+        <v>7.8421992791288986</v>
       </c>
       <c r="C9">
         <v>214.35566444654796</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>2.3159402215870051</v>
+        <v>2.0833038972044311</v>
       </c>
       <c r="B10">
-        <v>7.3060771759797429</v>
+        <v>7.4482701165368423</v>
       </c>
       <c r="C10">
         <v>214.35566444654796</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>1.6886905944904445</v>
+        <v>1.4615391371975073</v>
       </c>
       <c r="B11">
-        <v>6.910413765093212</v>
+        <v>7.04304944784867</v>
       </c>
       <c r="C11">
         <v>214.35566444654796</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>1.0706605531791265</v>
+        <v>0.84956919558363142</v>
       </c>
       <c r="B12">
-        <v>6.5045755734869291</v>
+        <v>6.627422506285968</v>
       </c>
       <c r="C12">
         <v>214.35566444654796</v>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>0.46335488469330477</v>
+        <v>0.24924622092134138</v>
       </c>
       <c r="B13">
-        <v>6.0869019107002673</v>
+        <v>6.19942152046893</v>
       </c>
       <c r="C13">
         <v>214.35566444654796</v>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-0.13234004481646683</v>
+        <v>-0.33833584037549308</v>
       </c>
       <c r="B14">
-        <v>5.6564145786417548</v>
+        <v>5.75788425293321</v>
       </c>
       <c r="C14">
         <v>214.35566444654796</v>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-0.72020504681064113</v>
+        <v>-0.91780121748847709</v>
       </c>
       <c r="B15">
-        <v>5.2172860996403614</v>
+        <v>5.307723606477726</v>
       </c>
       <c r="C15">
         <v>214.35566444654796</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-1.3037076973340498</v>
+        <v>-1.493391061772769</v>
       </c>
       <c r="B16">
-        <v>4.7733433078627359</v>
+        <v>4.85344549193543</v>
       </c>
       <c r="C16">
         <v>214.35566444654796</v>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-1.8803954531580776</v>
+        <v>-2.0620960376823141</v>
       </c>
       <c r="B17">
-        <v>4.3218795644057577</v>
+        <v>4.3918527120121276</v>
       </c>
       <c r="C17">
         <v>214.35566444654796</v>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-2.4470904568947129</v>
+        <v>-2.6200191405184947</v>
       </c>
       <c r="B18">
-        <v>3.8593877700531758</v>
+        <v>3.918804986341228</v>
       </c>
       <c r="C18">
         <v>214.35566444654796</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-3.0036337137918676</v>
+        <v>-3.1669631758737116</v>
       </c>
       <c r="B19">
-        <v>3.3856924574059386</v>
+        <v>3.434092810393659</v>
       </c>
       <c r="C19">
         <v>214.35566444654796</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-3.550620944756433</v>
+        <v>-3.7036559019131232</v>
       </c>
       <c r="B20">
-        <v>2.9014510670192886</v>
+        <v>2.9384893735997264</v>
       </c>
       <c r="C20">
         <v>214.35566444654796</v>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-4.0886478706953</v>
+        <v>-4.2308250768018842</v>
       </c>
       <c r="B21">
-        <v>2.4073210394484725</v>
+        <v>2.432767865389736</v>
       </c>
       <c r="C21">
         <v>214.35566444654796</v>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-4.6182028008721776</v>
+        <v>-4.7490675226636148</v>
       </c>
       <c r="B22">
-        <v>1.9038412752251823</v>
+        <v>1.9175623652970402</v>
       </c>
       <c r="C22">
         <v>214.35566444654796</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-5.1393443979780349</v>
+        <v>-5.2584563174557841</v>
       </c>
       <c r="B23">
-        <v>1.39107651478689</v>
+        <v>1.39295051326717</v>
       </c>
       <c r="C23">
         <v>214.35566444654796</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-5.6520239130606562</v>
+        <v>-5.7589336030943192</v>
       </c>
       <c r="B24">
-        <v>0.86897295854751566</v>
+        <v>0.858870839348705</v>
       </c>
       <c r="C24">
         <v>214.35566444654796</v>
@@ -1522,10 +1522,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-6.1561925971678306</v>
+        <v>-6.2504415214951532</v>
       </c>
       <c r="B25">
-        <v>0.33747680692097681</v>
+        <v>0.31526187359021868</v>
       </c>
       <c r="C25">
         <v>214.35566444654796</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-6.65178152266438</v>
+        <v>-6.73289811905897</v>
       </c>
       <c r="B26">
-        <v>-0.203488008973672</v>
+        <v>-0.23796345366933724</v>
       </c>
       <c r="C26">
         <v>214.35566444654796</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-7.1386410471832722</v>
+        <v>-7.2061250601254674</v>
       </c>
       <c r="B27">
-        <v>-0.754086635196829</v>
+        <v>-0.80099461092952162</v>
       </c>
       <c r="C27">
         <v>214.35566444654796</v>
@@ -1555,10 +1555,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-7.6166013496745109</v>
+        <v>-7.6699199135190916</v>
       </c>
       <c r="B28">
-        <v>-1.3145064871037584</v>
+        <v>-1.3740466663995214</v>
       </c>
       <c r="C28">
         <v>214.35566444654796</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-8.0854926090881</v>
+        <v>-8.1240802480642973</v>
       </c>
       <c r="B29">
-        <v>-1.8849349800497228</v>
+        <v>-1.9573346882885232</v>
       </c>
       <c r="C29">
         <v>214.35566444654796</v>
@@ -1577,10 +1577,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-8.5452195653261143</v>
+        <v>-8.568495629551423</v>
       </c>
       <c r="B30">
-        <v>-2.4654772435524941</v>
+        <v>-2.5509760048076484</v>
       </c>
       <c r="C30">
         <v>214.35566444654796</v>
@@ -1588,10 +1588,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-8.9959852020989342</v>
+        <v>-9.0034236116344</v>
       </c>
       <c r="B31">
-        <v>-3.055909263779899</v>
+        <v>-3.1546969841757773</v>
       </c>
       <c r="C31">
         <v>214.35566444654796</v>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-9.4380670640690223</v>
+        <v>-9.42921374493306</v>
       </c>
       <c r="B32">
-        <v>-3.6559247410622837</v>
+        <v>-3.7681262546137386</v>
       </c>
       <c r="C32">
         <v>214.35566444654796</v>
@@ -1610,10 +1610,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-9.87174269589883</v>
+        <v>-9.84621558006722</v>
       </c>
       <c r="B33">
-        <v>-4.2652173757299821</v>
+        <v>-4.3908924443423452</v>
       </c>
       <c r="C33">
         <v>214.35566444654796</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-10.297160202584223</v>
+        <v>-10.254620903531935</v>
       </c>
       <c r="B34">
-        <v>-4.8836237183730624</v>
+        <v>-5.0227917943411695</v>
       </c>
       <c r="C34">
         <v>214.35566444654796</v>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-10.713949930454717</v>
+        <v>-10.653990445323119</v>
       </c>
       <c r="B35">
-        <v>-5.5115517206204814</v>
+        <v>-5.6642909966247519</v>
       </c>
       <c r="C35">
         <v>214.35566444654796</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-11.121612786173241</v>
+        <v>-11.043727171311931</v>
       </c>
       <c r="B36">
-        <v>-6.1495521843609193</v>
+        <v>-6.3160243559663867</v>
       </c>
       <c r="C36">
         <v>214.35566444654796</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-11.519649676402729</v>
+        <v>-11.423234047369515</v>
       </c>
       <c r="B37">
-        <v>-6.7981759114830727</v>
+        <v>-6.9786261771393709</v>
       </c>
       <c r="C37">
         <v>214.35566444654796</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-11.907249415458205</v>
+        <v>-11.791532572944513</v>
       </c>
       <c r="B38">
-        <v>-7.4583181305427226</v>
+        <v>-7.6531360448850068</v>
       </c>
       <c r="C38">
         <v>214.35566444654796</v>
@@ -1676,10 +1676,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-12.282352448263129</v>
+        <v>-12.146118381795548</v>
       </c>
       <c r="B39">
-        <v>-8.1322517767641038</v>
+        <v>-8.342214663816673</v>
       </c>
       <c r="C39">
         <v>214.35566444654796</v>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-12.642587127393066</v>
+        <v>-12.48410564125874</v>
       </c>
       <c r="B40">
-        <v>-8.82259421203856</v>
+        <v>-9.0489280185157543</v>
       </c>
       <c r="C40">
         <v>214.35566444654796</v>
@@ -1698,10 +1698,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-12.985581805423569</v>
+        <v>-12.802608518670198</v>
       </c>
       <c r="B41">
-        <v>-9.5319627982574175</v>
+        <v>-9.7763420935636365</v>
       </c>
       <c r="C41">
         <v>214.35566444654796</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-12.985581805423569</v>
+        <v>-12.802608518670198</v>
       </c>
       <c r="B42">
-        <v>-9.5319627982574175</v>
+        <v>-9.7763420935636365</v>
       </c>
       <c r="C42">
         <v>214.35566444654796</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-12.53495013249379</v>
+        <v>-12.352263030722753</v>
       </c>
       <c r="B43">
-        <v>-8.941382934866656</v>
+        <v>-9.1890010782369149</v>
       </c>
       <c r="C43">
         <v>214.35566444654796</v>
@@ -1731,10 +1731,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-12.085564261061938</v>
+        <v>-11.905076086369816</v>
       </c>
       <c r="B44">
-        <v>-8.34942819874765</v>
+        <v>-8.5983043430579542</v>
       </c>
       <c r="C44">
         <v>214.35566444654796</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-11.635240206734046</v>
+        <v>-11.458353407160667</v>
       </c>
       <c r="B45">
-        <v>-7.758508845938116</v>
+        <v>-8.007114360370112</v>
       </c>
       <c r="C45">
         <v>214.35566444654796</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-11.181793985116137</v>
+        <v>-11.009400714644583</v>
       </c>
       <c r="B46">
-        <v>-7.1710351324757609</v>
+        <v>-7.4182936025167274</v>
       </c>
       <c r="C46">
         <v>214.35566444654796</v>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-10.723345770110976</v>
+        <v>-10.555897098230062</v>
       </c>
       <c r="B47">
-        <v>-6.5890816437894815</v>
+        <v>-6.8343078659999152</v>
       </c>
       <c r="C47">
         <v>214.35566444654796</v>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-10.259232368808327</v>
+        <v>-10.097015118762595</v>
       </c>
       <c r="B48">
-        <v>-6.01338028287296</v>
+        <v>-6.2560362439568422</v>
       </c>
       <c r="C48">
         <v>214.35566444654796</v>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-9.7890947465946887</v>
+        <v>-9.6323007049468785</v>
       </c>
       <c r="B49">
-        <v>-5.4443272821110487</v>
+        <v>-5.68396115368343</v>
       </c>
       <c r="C49">
         <v>214.35566444654796</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-9.31257386885656</v>
+        <v>-9.1612997854876266</v>
       </c>
       <c r="B50">
-        <v>-4.8823188738886119</v>
+        <v>-5.118565012475603</v>
       </c>
       <c r="C50">
         <v>214.35566444654796</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-8.8294324580999177</v>
+        <v>-8.6837082113700141</v>
       </c>
       <c r="B51">
-        <v>-4.3276169188279994</v>
+        <v>-4.5601709562523629</v>
       </c>
       <c r="C51">
         <v>214.35566444654796</v>
@@ -1819,10 +1819,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-8.3399202653085958</v>
+        <v>-8.19982152270107</v>
       </c>
       <c r="B52">
-        <v>-3.77994579050148</v>
+        <v>-4.0084649954249487</v>
       </c>
       <c r="C52">
         <v>214.35566444654796</v>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-7.8444087985859063</v>
+        <v>-7.7100851818682932</v>
       </c>
       <c r="B53">
-        <v>-3.2388954907188157</v>
+        <v>-3.4629738590276857</v>
       </c>
       <c r="C53">
         <v>214.35566444654796</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-7.3432695660351524</v>
+        <v>-7.2149446512591728</v>
       </c>
       <c r="B54">
-        <v>-2.7040560212897558</v>
+        <v>-2.9232242760948792</v>
       </c>
       <c r="C54">
         <v>214.35566444654796</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-6.83679296459898</v>
+        <v>-6.7147467102685043</v>
       </c>
       <c r="B55">
-        <v>-2.1751068987043047</v>
+        <v>-2.3888478190697593</v>
       </c>
       <c r="C55">
         <v>214.35566444654796</v>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-6.3249449465774248</v>
+        <v>-6.20944340632032</v>
       </c>
       <c r="B56">
-        <v>-1.6520856981734684</v>
+        <v>-1.8598954340312306</v>
       </c>
       <c r="C56">
         <v>214.35566444654796</v>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-5.8076103531098537</v>
+        <v>-5.6988881038459454</v>
       </c>
       <c r="B57">
-        <v>-1.1351195095884994</v>
+        <v>-1.3365229104671037</v>
       </c>
       <c r="C57">
         <v>214.35566444654796</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-5.2846740253356357</v>
+        <v>-5.1829341672767111</v>
       </c>
       <c r="B58">
-        <v>-0.62433542284064847</v>
+        <v>-0.818886037865195</v>
       </c>
       <c r="C58">
         <v>214.35566444654796</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-4.756034899333426</v>
+        <v>-4.6614528466694178</v>
       </c>
       <c r="B59">
-        <v>-0.11984497257608523</v>
+        <v>-0.30712160355404228</v>
       </c>
       <c r="C59">
         <v>214.35566444654796</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-4.2216482909390054</v>
+        <v>-4.1343869345827553</v>
       </c>
       <c r="B60">
-        <v>0.37830252753935212</v>
+        <v>0.19870961377492286</v>
       </c>
       <c r="C60">
         <v>214.35566444654796</v>
@@ -1918,10 +1918,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-3.6814836109274336</v>
+        <v>-3.6016971092008823</v>
       </c>
       <c r="B61">
-        <v>0.8700733190849107</v>
+        <v>0.69856583758954827</v>
       </c>
       <c r="C61">
         <v>214.35566444654796</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-3.1355102700737771</v>
+        <v>-3.0633440487079628</v>
       </c>
       <c r="B62">
-        <v>1.3554336436398344</v>
+        <v>1.1924052913576779</v>
       </c>
       <c r="C62">
         <v>214.35566444654796</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-2.5837989134849595</v>
+        <v>-2.5194130619321609</v>
       </c>
       <c r="B63">
-        <v>1.8344614654954263</v>
+        <v>1.6803186094238027</v>
       </c>
       <c r="C63">
         <v>214.35566444654796</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-2.0268251235953478</v>
+        <v>-1.9704879802776407</v>
       </c>
       <c r="B64">
-        <v>2.3076816397912343</v>
+        <v>2.1629260696389956</v>
       </c>
       <c r="C64">
         <v>214.35566444654796</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-1.4651657171711721</v>
+        <v>-1.4172772657925743</v>
       </c>
       <c r="B65">
-        <v>2.7757307443788619</v>
+        <v>2.6409803607309765</v>
       </c>
       <c r="C65">
         <v>214.35566444654796</v>
@@ -1973,10 +1973,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-0.89939751097865928</v>
+        <v>-0.86048938052512924</v>
       </c>
       <c r="B66">
-        <v>3.2392453571099171</v>
+        <v>3.1152341714274647</v>
       </c>
       <c r="C66">
         <v>214.35566444654796</v>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-0.32933756077623738</v>
+        <v>-0.299902683986866</v>
       </c>
       <c r="B67">
-        <v>3.6980235798096497</v>
+        <v>3.5854520250396424</v>
       </c>
       <c r="C67">
         <v>214.35566444654796</v>
@@ -1995,10 +1995,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>0.24823612170888082</v>
+        <v>0.26842487445709612</v>
       </c>
       <c r="B68">
-        <v>4.1485096101979071</v>
+        <v>4.047445783212547</v>
       </c>
       <c r="C68">
         <v>214.35566444654796</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>0.83582760779070786</v>
+        <v>0.84755522687024742</v>
       </c>
       <c r="B69">
-        <v>4.5879399427203076</v>
+        <v>4.4979623687274666</v>
       </c>
       <c r="C69">
         <v>214.35566444654796</v>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>1.4300302569169037</v>
+        <v>1.4333094208840314</v>
       </c>
       <c r="B70">
-        <v>5.0200741628309462</v>
+        <v>4.9414416105768035</v>
       </c>
       <c r="C70">
         <v>214.35566444654796</v>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>2.0271300572803908</v>
+        <v>2.0211314120573847</v>
       </c>
       <c r="B71">
-        <v>5.4490110724291565</v>
+        <v>5.3827239702964089</v>
       </c>
       <c r="C71">
         <v>214.35566444654796</v>
@@ -2039,10 +2039,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>2.6280942239214551</v>
+        <v>2.6121976720912272</v>
       </c>
       <c r="B72">
-        <v>5.8736832481867145</v>
+        <v>5.8205595333847979</v>
       </c>
       <c r="C72">
         <v>214.35566444654796</v>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>3.2345153443196248</v>
+        <v>3.2084499705206819</v>
       </c>
       <c r="B73">
-        <v>6.29233310264159</v>
+        <v>6.2528853127776713</v>
       </c>
       <c r="C73">
         <v>214.35566444654796</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>3.8458062688640338</v>
+        <v>3.8091587520757262</v>
       </c>
       <c r="B74">
-        <v>6.7056086170241125</v>
+        <v>6.6804764071968536</v>
       </c>
       <c r="C74">
         <v>214.35566444654796</v>
@@ -2072,10 +2072,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>4.4608247812386015</v>
+        <v>4.4129138414992939</v>
       </c>
       <c r="B75">
-        <v>7.1147703469407224</v>
+        <v>7.1048310239533</v>
       </c>
       <c r="C75">
         <v>214.35566444654796</v>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>5.0783881353967848</v>
+        <v>5.0182539083912951</v>
       </c>
       <c r="B76">
-        <v>7.5211235768099467</v>
+        <v>7.5275017189283879</v>
       </c>
       <c r="C76">
         <v>214.35566444654796</v>
@@ -2094,10 +2094,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>5.6974096285400382</v>
+        <v>5.6238344596824446</v>
       </c>
       <c r="B77">
-        <v>7.9258675972442152</v>
+        <v>7.9499169169479238</v>
       </c>
       <c r="C77">
         <v>214.35566444654796</v>
@@ -2105,10 +2105,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>6.3172272605922712</v>
+        <v>6.228829506769701</v>
       </c>
       <c r="B78">
-        <v>8.32973299481949</v>
+        <v>8.3729541700449914</v>
       </c>
       <c r="C78">
         <v>214.35566444654796</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>6.9366653691212576</v>
+        <v>6.8317830900687531</v>
       </c>
       <c r="B79">
-        <v>8.7340172364423161</v>
+        <v>8.7981603280049185</v>
       </c>
       <c r="C79">
         <v>214.35566444654796</v>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>7.5536118519183555</v>
+        <v>7.430090572262344</v>
       </c>
       <c r="B80">
-        <v>9.1410512486132109</v>
+        <v>9.2283026260713736</v>
       </c>
       <c r="C80">
         <v>214.35566444654796</v>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>8.1627638114807386</v>
+        <v>8.0172376277883135</v>
       </c>
       <c r="B81">
-        <v>9.5566873353865418</v>
+        <v>9.6703020551880421</v>
       </c>
       <c r="C81">
         <v>214.35566444654796</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>8.667102340493253</v>
+        <v>8.4743671577408541</v>
       </c>
       <c r="B82">
-        <v>10.087996045330947</v>
+        <v>10.25043552572278</v>
       </c>
       <c r="C82">
         <v>214.35566444654796</v>
@@ -2170,10 +2170,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>9.034723639427062</v>
+        <v>8.8116934975571919</v>
       </c>
       <c r="B1">
-        <v>11.281202010095971</v>
+        <v>11.456275127008654</v>
       </c>
       <c r="C1">
         <v>232.84072182980668</v>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>8.01323328578643</v>
+        <v>7.70877537571661</v>
       </c>
       <c r="B2">
-        <v>11.195771216402489</v>
+        <v>11.433640577266791</v>
       </c>
       <c r="C2">
         <v>232.84072182980668</v>
@@ -2192,10 +2192,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>7.17857853581609</v>
+        <v>6.8482253834663123</v>
       </c>
       <c r="B3">
-        <v>10.917172153512832</v>
+        <v>11.170062086243753</v>
       </c>
       <c r="C3">
         <v>232.84072182980668</v>
@@ -2203,10 +2203,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>6.3776950365567915</v>
+        <v>6.0293290710479761</v>
       </c>
       <c r="B4">
-        <v>10.603657186372097</v>
+        <v>10.865074678113738</v>
       </c>
       <c r="C4">
         <v>232.84072182980668</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>5.6019762602837551</v>
+        <v>5.2408306157453044</v>
       </c>
       <c r="B5">
-        <v>10.264124555100095</v>
+        <v>10.52986803483787</v>
       </c>
       <c r="C5">
         <v>232.84072182980668</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>4.8478588279799055</v>
+        <v>4.4780861677948121</v>
       </c>
       <c r="B6">
-        <v>9.9022584170185244</v>
+        <v>10.169058718282681</v>
       </c>
       <c r="C6">
         <v>232.84072182980668</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>4.1132764403428377</v>
+        <v>3.7384125438655254</v>
       </c>
       <c r="B7">
-        <v>9.5201951072372228</v>
+        <v>9.7853141450265841</v>
       </c>
       <c r="C7">
         <v>232.84072182980668</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>3.3969824959224728</v>
+        <v>3.0202002719092502</v>
       </c>
       <c r="B8">
-        <v>9.1192234799133089</v>
+        <v>9.3802343296396753</v>
       </c>
       <c r="C8">
         <v>232.84072182980668</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>2.6970846419740728</v>
+        <v>2.3209900637304175</v>
       </c>
       <c r="B9">
-        <v>8.70130002779886</v>
+        <v>8.95626410920342</v>
       </c>
       <c r="C9">
         <v>232.84072182980668</v>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>2.0115501503770807</v>
+        <v>1.638137162478617</v>
       </c>
       <c r="B10">
-        <v>8.2685263769495041</v>
+        <v>8.5160326996149163</v>
       </c>
       <c r="C10">
         <v>232.84072182980668</v>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>1.3384305428023311</v>
+        <v>0.969104752831444</v>
       </c>
       <c r="B11">
-        <v>7.8229170480402024</v>
+        <v>8.0620620095224442</v>
       </c>
       <c r="C11">
         <v>232.84072182980668</v>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>0.67666132628855813</v>
+        <v>0.31251416397909532</v>
       </c>
       <c r="B12">
-        <v>7.3655726142960729</v>
+        <v>7.5957226084773906</v>
       </c>
       <c r="C12">
         <v>232.84072182980668</v>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>0.028629699554723245</v>
+        <v>-0.32848863836583592</v>
       </c>
       <c r="B13">
-        <v>6.894024964523588</v>
+        <v>7.1138870168923738</v>
       </c>
       <c r="C13">
         <v>232.84072182980668</v>
@@ -2313,10 +2313,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-0.60425241835786569</v>
+        <v>-0.95203799618252161</v>
       </c>
       <c r="B14">
-        <v>6.406814323647243</v>
+        <v>6.6147005396084966</v>
       </c>
       <c r="C14">
         <v>232.84072182980668</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-1.2279259187987119</v>
+        <v>-1.5659141187395653</v>
       </c>
       <c r="B15">
-        <v>5.910082945482273</v>
+        <v>6.1058976683196056</v>
       </c>
       <c r="C15">
         <v>232.84072182980668</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-1.8478395575164546</v>
+        <v>-2.1772527714644236</v>
       </c>
       <c r="B16">
-        <v>5.4094642676420754</v>
+        <v>5.5945722377186389</v>
       </c>
       <c r="C16">
         <v>232.84072182980668</v>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-2.460120737465469</v>
+        <v>-2.78096607713055</v>
       </c>
       <c r="B17">
-        <v>4.9009544340419229</v>
+        <v>5.0756662676421458</v>
       </c>
       <c r="C17">
         <v>232.84072182980668</v>
@@ -2357,10 +2357,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-3.0597560791920611</v>
+        <v>-3.3704712548020006</v>
       </c>
       <c r="B18">
-        <v>4.37937014014634</v>
+        <v>4.5426356584761329</v>
       </c>
       <c r="C18">
         <v>232.84072182980668</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-3.6464904264045526</v>
+        <v>-3.9454295513592865</v>
       </c>
       <c r="B19">
-        <v>3.8444475813149404</v>
+        <v>3.9951436476608211</v>
       </c>
       <c r="C19">
         <v>232.84072182980668</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-4.2212581786017767</v>
+        <v>-4.5070632206370389</v>
       </c>
       <c r="B20">
-        <v>3.2971528278811095</v>
+        <v>3.4344053068999765</v>
       </c>
       <c r="C20">
         <v>232.84072182980668</v>
@@ -2390,10 +2390,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-4.7849937352825584</v>
+        <v>-5.056594516469878</v>
       </c>
       <c r="B21">
-        <v>2.7384519501782383</v>
+        <v>2.861635707897372</v>
       </c>
       <c r="C21">
         <v>232.84072182980668</v>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-5.3384635700091385</v>
+        <v>-5.5950265115825433</v>
       </c>
       <c r="B22">
-        <v>2.1691374008678812</v>
+        <v>2.27783202918509</v>
       </c>
       <c r="C22">
         <v>232.84072182980668</v>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-5.8817624525973908</v>
+        <v>-6.1224855542601908</v>
       </c>
       <c r="B23">
-        <v>1.5893071619242694</v>
+        <v>1.6831198766084718</v>
       </c>
       <c r="C23">
         <v>232.84072182980668</v>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-6.41481722692659</v>
+        <v>-6.6388788116780866</v>
       </c>
       <c r="B24">
-        <v>0.99888559764980611</v>
+        <v>1.0774069628411727</v>
       </c>
       <c r="C24">
         <v>232.84072182980668</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-6.9375547368760255</v>
+        <v>-7.1441134510115027</v>
       </c>
       <c r="B25">
-        <v>0.39779707234688466</v>
+        <v>0.46060100055684072</v>
       </c>
       <c r="C25">
         <v>232.84072182980668</v>
@@ -2445,10 +2445,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-7.4498712566362491</v>
+        <v>-7.63805759027762</v>
       </c>
       <c r="B26">
-        <v>-0.21406565550959347</v>
+        <v>-0.16742911727074453</v>
       </c>
       <c r="C26">
         <v>232.84072182980668</v>
@@ -2456,10 +2456,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-7.9515407816429136</v>
+        <v>-8.12042315086132</v>
       </c>
       <c r="B27">
-        <v>-0.83693625075475331</v>
+        <v>-0.80696977646733514</v>
       </c>
       <c r="C27">
         <v>232.84072182980668</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-8.442306737642939</v>
+        <v>-8.5908830049893865</v>
       </c>
       <c r="B28">
-        <v>-1.4710799840512112</v>
+        <v>-1.458346182558556</v>
       </c>
       <c r="C28">
         <v>232.84072182980668</v>
@@ -2478,10 +2478,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-8.92191255038325</v>
+        <v>-9.0491100248886216</v>
       </c>
       <c r="B29">
-        <v>-2.1167621260615954</v>
+        <v>-2.1218835410700381</v>
       </c>
       <c r="C29">
         <v>232.84072182980668</v>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-9.3902203597631413</v>
+        <v>-9.4949339066925162</v>
       </c>
       <c r="B30">
-        <v>-2.7741252095608213</v>
+        <v>-2.7977511551394509</v>
       </c>
       <c r="C30">
         <v>232.84072182980668</v>
@@ -2500,10 +2500,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-9.8475671622913836</v>
+        <v>-9.928811642161353</v>
       </c>
       <c r="B31">
-        <v>-3.4428208157729827</v>
+        <v>-3.4854947183526477</v>
       </c>
       <c r="C31">
         <v>232.84072182980668</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-10.294408668629135</v>
+        <v>-10.35135704696213</v>
       </c>
       <c r="B32">
-        <v>-4.1223777880344832</v>
+        <v>-4.1845040219075385</v>
       </c>
       <c r="C32">
         <v>232.84072182980668</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-10.731200589437536</v>
+        <v>-10.763183936761829</v>
       </c>
       <c r="B33">
-        <v>-4.8123249696817121</v>
+        <v>-4.894168857002021</v>
       </c>
       <c r="C33">
         <v>232.84072182980668</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-11.158196287866629</v>
+        <v>-11.164642068156715</v>
       </c>
       <c r="B34">
-        <v>-5.512400409993238</v>
+        <v>-5.6141415222574693</v>
       </c>
       <c r="C34">
         <v>232.84072182980668</v>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-11.574839737021993</v>
+        <v>-11.555024961460182</v>
       </c>
       <c r="B35">
-        <v>-6.2231789820163286</v>
+        <v>-6.3451243459891389</v>
       </c>
       <c r="C35">
         <v>232.84072182980668</v>
@@ -2555,10 +2555,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-11.980372562498102</v>
+        <v>-11.933362077914891</v>
       </c>
       <c r="B36">
-        <v>-6.945444764740424</v>
+        <v>-7.0880821639357565</v>
       </c>
       <c r="C36">
         <v>232.84072182980668</v>
@@ -2566,10 +2566,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-12.374036389889447</v>
+        <v>-12.298682878763517</v>
       </c>
       <c r="B37">
-        <v>-7.6799818371549744</v>
+        <v>-7.843979811836058</v>
       </c>
       <c r="C37">
         <v>232.84072182980668</v>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-12.754582877683113</v>
+        <v>-12.649375593129445</v>
       </c>
       <c r="B38">
-        <v>-8.4280808524581676</v>
+        <v>-8.6144195895803346</v>
       </c>
       <c r="C38">
         <v>232.84072182980668</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-13.118803815936687</v>
+        <v>-12.981263521658939</v>
       </c>
       <c r="B39">
-        <v>-9.19305876068319</v>
+        <v>-9.4035536536651421</v>
       </c>
       <c r="C39">
         <v>232.84072182980668</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-13.463001027600372</v>
+        <v>-13.289528732878978</v>
       </c>
       <c r="B40">
-        <v>-9.9787390860719771</v>
+        <v>-10.216171624738591</v>
       </c>
       <c r="C40">
         <v>232.84072182980668</v>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-13.783476335624377</v>
+        <v>-13.569353295316548</v>
       </c>
       <c r="B41">
-        <v>-10.788945352866458</v>
+        <v>-11.0570631234488</v>
       </c>
       <c r="C41">
         <v>232.84072182980668</v>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-13.783476335624377</v>
+        <v>-13.569353295316548</v>
       </c>
       <c r="B42">
-        <v>-10.78894535286646</v>
+        <v>-11.0570631234488</v>
       </c>
       <c r="C42">
         <v>232.84072182980668</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-13.293490474530396</v>
+        <v>-13.067210094560339</v>
       </c>
       <c r="B43">
-        <v>-10.153995083878469</v>
+        <v>-10.43718388830356</v>
       </c>
       <c r="C43">
         <v>232.84072182980668</v>
@@ -2643,10 +2643,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-12.80889480666597</v>
+        <v>-12.57480771288518</v>
       </c>
       <c r="B44">
-        <v>-9.5134719247328619</v>
+        <v>-9.8076210724636823</v>
       </c>
       <c r="C44">
         <v>232.84072182980668</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-12.326213138690438</v>
+        <v>-12.087554660184654</v>
       </c>
       <c r="B45">
-        <v>-8.8709698919758182</v>
+        <v>-9.1729391858111544</v>
       </c>
       <c r="C45">
         <v>232.84072182980668</v>
@@ -2665,10 +2665,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-11.841969277263148</v>
+        <v>-11.600859446352336</v>
       </c>
       <c r="B46">
-        <v>-8.2300830021535152</v>
+        <v>-8.5377027382279724</v>
       </c>
       <c r="C46">
         <v>232.84072182980668</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-11.353167555284566</v>
+        <v>-11.110762182952701</v>
       </c>
       <c r="B47">
-        <v>-7.593908458461363</v>
+        <v>-7.9058483493031213</v>
       </c>
       <c r="C47">
         <v>232.84072182980668</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-10.858734410619675</v>
+        <v>-10.615829388233742</v>
       </c>
       <c r="B48">
-        <v>-6.9635562106917188</v>
+        <v>-7.2788010774535952</v>
       </c>
       <c r="C48">
         <v>232.84072182980668</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-10.358076807374564</v>
+        <v>-10.115259182114334</v>
       </c>
       <c r="B49">
-        <v>-6.3396393952861558</v>
+        <v>-6.6573580908033732</v>
       </c>
       <c r="C49">
         <v>232.84072182980668</v>
@@ -2709,10 +2709,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-9.8506017096553364</v>
+        <v>-9.60824968451336</v>
       </c>
       <c r="B50">
-        <v>-5.722771148686264</v>
+        <v>-6.042316557476445</v>
       </c>
       <c r="C50">
         <v>232.84072182980668</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-9.33590932765539</v>
+        <v>-9.0942537902308072</v>
       </c>
       <c r="B51">
-        <v>-5.1133648113018335</v>
+        <v>-5.4342203678077743</v>
       </c>
       <c r="C51">
         <v>232.84072182980668</v>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-8.8143728559172878</v>
+        <v>-8.5737434935910617</v>
       </c>
       <c r="B52">
-        <v>-4.5110345394154781</v>
+        <v>-4.83260030097624</v>
       </c>
       <c r="C52">
         <v>232.84072182980668</v>
@@ -2742,10 +2742,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-8.2865587350708854</v>
+        <v>-8.0474455637996218</v>
       </c>
       <c r="B53">
-        <v>-3.9151946932780195</v>
+        <v>-4.2367338583716947</v>
       </c>
       <c r="C53">
         <v>232.84072182980668</v>
@@ -2753,10 +2753,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-7.7530334057460335</v>
+        <v>-7.5160867700619729</v>
       </c>
       <c r="B54">
-        <v>-3.32525963314027</v>
+        <v>-3.645898541383982</v>
       </c>
       <c r="C54">
         <v>232.84072182980668</v>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-7.2142368647664759</v>
+        <v>-6.9802291728039023</v>
       </c>
       <c r="B55">
-        <v>-2.7407744487858468</v>
+        <v>-3.0595355923313274</v>
       </c>
       <c r="C55">
         <v>232.84072182980668</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-6.6701033337315145</v>
+        <v>-6.4397759973323732</v>
       </c>
       <c r="B56">
-        <v>-2.1618071481295411</v>
+        <v>-2.4777412172454309</v>
       </c>
       <c r="C56">
         <v>232.84072182980668</v>
@@ -2786,10 +2786,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-6.1204405904343329</v>
+        <v>-5.8944657601746275</v>
       </c>
       <c r="B57">
-        <v>-1.5885564686189342</v>
+        <v>-1.900775363086356</v>
       </c>
       <c r="C57">
         <v>232.84072182980668</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-5.5650564126681186</v>
+        <v>-5.3440369778579262</v>
       </c>
       <c r="B58">
-        <v>-1.0212211477016135</v>
+        <v>-1.3288979768141715</v>
       </c>
       <c r="C58">
         <v>232.84072182980668</v>
@@ -2808,10 +2808,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-5.0037819838519333</v>
+        <v>-4.7882599081431128</v>
       </c>
       <c r="B59">
-        <v>-0.45997572388153551</v>
+        <v>-0.76233745067117542</v>
       </c>
       <c r="C59">
         <v>232.84072182980668</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-4.4365421099083493</v>
+        <v>-4.2270317737254386</v>
       </c>
       <c r="B60">
-        <v>0.095102060111827535</v>
+        <v>-0.20119595802861254</v>
       </c>
       <c r="C60">
         <v>232.84072182980668</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-3.8632850023858083</v>
+        <v>-3.6602815385337433</v>
       </c>
       <c r="B61">
-        <v>0.64395866049263462</v>
+        <v>0.35445588246004561</v>
       </c>
       <c r="C61">
         <v>232.84072182980668</v>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-3.2839588728327573</v>
+        <v>-3.0879381664968757</v>
       </c>
       <c r="B62">
-        <v>1.1865405334750403</v>
+        <v>0.90454745214132148</v>
       </c>
       <c r="C62">
         <v>232.84072182980668</v>
@@ -2852,10 +2852,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-2.6986725899347346</v>
+        <v>-2.5101423878892266</v>
       </c>
       <c r="B63">
-        <v>1.7229602377745181</v>
+        <v>1.4492186543392425</v>
       </c>
       <c r="C63">
         <v>232.84072182980668</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-2.1081776509256285</v>
+        <v>-1.9278819983673554</v>
       </c>
       <c r="B64">
-        <v>2.253994742111836</v>
+        <v>1.9894514802878722</v>
       </c>
       <c r="C64">
         <v>232.84072182980668</v>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-1.5133862101764237</v>
+        <v>-1.3423565599333718</v>
       </c>
       <c r="B65">
-        <v>2.7805871177090746</v>
+        <v>2.5264384431987708</v>
       </c>
       <c r="C65">
         <v>232.84072182980668</v>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-0.915210422058099</v>
+        <v>-0.75476563458937962</v>
       </c>
       <c r="B66">
-        <v>3.3036804357883227</v>
+        <v>3.0613720562835089</v>
       </c>
       <c r="C66">
         <v>232.84072182980668</v>
@@ -2896,10 +2896,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-0.31336694522045444</v>
+        <v>-0.16474171817287658</v>
       </c>
       <c r="B67">
-        <v>3.8229817513373057</v>
+        <v>3.5938869748843492</v>
       </c>
       <c r="C67">
         <v>232.84072182980668</v>
@@ -2907,10 +2907,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>0.29720954457144405</v>
+        <v>0.4343509581370788</v>
       </c>
       <c r="B68">
-        <v>4.3332540544063178</v>
+        <v>4.1173864228663577</v>
       </c>
       <c r="C68">
         <v>232.84072182980668</v>
@@ -2918,10 +2918,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>0.92045230246305021</v>
+        <v>1.047662147742878</v>
       </c>
       <c r="B69">
-        <v>4.83043077484584</v>
+        <v>4.6267509074831343</v>
       </c>
       <c r="C69">
         <v>232.84072182980668</v>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>1.5509843243571453</v>
+        <v>1.668129277714234</v>
       </c>
       <c r="B70">
-        <v>5.3200711666444906</v>
+        <v>5.129001501019574</v>
       </c>
       <c r="C70">
         <v>232.84072182980668</v>
@@ -2940,10 +2940,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>2.1829433883852389</v>
+        <v>2.2880523880263262</v>
       </c>
       <c r="B71">
-        <v>5.8082361476880218</v>
+        <v>5.6317929174812837</v>
       </c>
       <c r="C71">
         <v>232.84072182980668</v>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>2.817836660836428</v>
+        <v>2.9093942966088684</v>
       </c>
       <c r="B72">
-        <v>6.2933674673125557</v>
+        <v>6.1331738727254139</v>
       </c>
       <c r="C72">
         <v>232.84072182980668</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>3.4581547981232919</v>
+        <v>3.5354065044032308</v>
       </c>
       <c r="B73">
-        <v>6.7728900500028786</v>
+        <v>6.6299119720752433</v>
       </c>
       <c r="C73">
         <v>232.84072182980668</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>4.10295302899478</v>
+        <v>4.1648324664428831</v>
       </c>
       <c r="B74">
-        <v>7.2477806893880823</v>
+        <v>7.1232563768670616</v>
       </c>
       <c r="C74">
         <v>232.84072182980668</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>4.7504110457761772</v>
+        <v>4.7952661118562911</v>
       </c>
       <c r="B75">
-        <v>7.7199213912316331</v>
+        <v>7.6155990195705785</v>
       </c>
       <c r="C75">
         <v>232.84072182980668</v>
@@ -2995,10 +2995,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>5.3986418227617694</v>
+        <v>5.4242113120597795</v>
       </c>
       <c r="B76">
-        <v>8.191263140690225</v>
+        <v>8.1094213611761976</v>
       </c>
       <c r="C76">
         <v>232.84072182980668</v>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>6.0459080542573735</v>
+        <v>6.0493669394099729</v>
       </c>
       <c r="B77">
-        <v>8.6636021282512043</v>
+        <v>8.6070110075862427</v>
       </c>
       <c r="C77">
         <v>232.84072182980668</v>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>6.6911380326459513</v>
+        <v>6.6693019277368295</v>
       </c>
       <c r="B78">
-        <v>9.1380463863313057</v>
+        <v>9.10979061583003</v>
       </c>
       <c r="C78">
         <v>232.84072182980668</v>
@@ -3028,10 +3028,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>7.3324496114785465</v>
+        <v>7.28152094453842</v>
       </c>
       <c r="B79">
-        <v>9.61654185545137</v>
+        <v>9.6202408554941</v>
       </c>
       <c r="C79">
         <v>232.84072182980668</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>7.9664827966738487</v>
+        <v>7.8815876091623078</v>
       </c>
       <c r="B80">
-        <v>10.102562414403495</v>
+        <v>10.14277203845085</v>
       </c>
       <c r="C80">
         <v>232.84072182980668</v>
@@ -3050,10 +3050,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>8.58485010248716</v>
+        <v>8.4584695394568428</v>
       </c>
       <c r="B81">
-        <v>10.604779837048659</v>
+        <v>10.688351719064094</v>
       </c>
       <c r="C81">
         <v>232.84072182980668</v>
@@ -3061,10 +3061,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>9.034723639427062</v>
+        <v>8.8116934975571919</v>
       </c>
       <c r="B82">
-        <v>11.281202010095971</v>
+        <v>11.456275127008654</v>
       </c>
       <c r="C82">
         <v>232.84072182980668</v>
